--- a/LULU/model18_humanized.xlsx
+++ b/LULU/model18_humanized.xlsx
@@ -1115,14 +1115,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="B2:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1130,7 +1129,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -1145,7 +1143,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -1153,7 +1150,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -1175,7 +1171,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -1197,7 +1192,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="36" customHeight="1">
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -1205,7 +1199,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="11" t="inlineStr">
         <is>
@@ -1233,7 +1226,7 @@
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
     <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="2" max="2"/>
-    <col hidden="1" outlineLevel="1" width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col hidden="1" outlineLevel="1" width="40" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1314,7 +1307,6 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -1426,7 +1418,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
@@ -1644,7 +1635,6 @@
         <v/>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
@@ -1680,7 +1670,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -1768,7 +1757,7 @@
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col hidden="1" outlineLevel="1" width="26" customWidth="1" min="2" max="2"/>
-    <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col hidden="1" outlineLevel="1" width="38" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -2245,7 +2234,6 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4248,7 +4236,6 @@
         <v/>
       </c>
     </row>
-    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4306,7 +4293,6 @@
         <v/>
       </c>
     </row>
-    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="inlineStr">
         <is>
@@ -4314,7 +4300,6 @@
         </is>
       </c>
     </row>
-    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -5400,10 +5385,10 @@
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col hidden="1" outlineLevel="1" width="40" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
     <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="10" max="10"/>
     <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="11" max="11"/>
-    <col hidden="1" outlineLevel="1" width="36" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6111,7 +6096,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6591,7 +6575,6 @@
       </c>
       <c r="L34" s="19" t="n"/>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -6795,7 +6778,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7147,7 +7129,6 @@
       </c>
       <c r="L51" s="19" t="n"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -7435,7 +7416,7 @@
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
     <col hidden="1" outlineLevel="1" width="22" customWidth="1" min="2" max="2"/>
-    <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -7510,7 +7491,6 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -7717,7 +7697,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" hidden="1" outlineLevel="1">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -8511,7 +8490,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" hidden="1" outlineLevel="1" ht="28" customHeight="1">
+    <row r="41" ht="28" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
         <is>
           <t>NORMALIZED NOPAT</t>
@@ -8545,7 +8524,6 @@
         <v/>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="61" t="inlineStr">
         <is>
@@ -8621,7 +8599,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1"/>
+    <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M104"/>
@@ -8629,7 +8607,7 @@
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col hidden="1" outlineLevel="1" width="26" customWidth="1" min="2" max="2"/>
-    <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col hidden="1" outlineLevel="1" width="36" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -8638,8 +8616,8 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="8" customWidth="1" min="11" max="11"/>
-    <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="12" max="12"/>
-    <col hidden="1" outlineLevel="1" width="36" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="16" customHeight="1">
@@ -8742,7 +8720,11 @@
 Ctrl+F: 5-phase EBIT normalization → normalized NOPAT (base case).</t>
         </is>
       </c>
-      <c r="D4" s="85" t="n"/>
+      <c r="D4" s="85" t="inlineStr">
+        <is>
+          <t>'Revenue Drivers'!A1</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="16" t="inlineStr">
@@ -9888,7 +9870,6 @@
         <v/>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
@@ -10131,8 +10112,6 @@
         <v/>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -10151,7 +10130,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
@@ -10212,7 +10190,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -10297,7 +10274,6 @@
         <v/>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -10418,7 +10394,6 @@
         <v/>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -10479,7 +10454,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="inlineStr">
         <is>
@@ -10513,7 +10487,11 @@
         <f>E46</f>
         <v/>
       </c>
-      <c r="M82" s="95" t="n"/>
+      <c r="M82" s="95" t="inlineStr">
+        <is>
+          <t>'Comps'!A45</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
@@ -10559,7 +10537,6 @@
         <v/>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -10666,8 +10643,6 @@
       </c>
       <c r="D94" s="26" t="n"/>
     </row>
-    <row r="95"/>
-    <row r="96"/>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -10971,7 +10946,7 @@
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="2" max="2"/>
-    <col hidden="1" outlineLevel="1" width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col hidden="1" outlineLevel="1" width="44" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
@@ -11140,7 +11115,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -11462,7 +11436,6 @@
         <v>407521</v>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
@@ -11549,7 +11522,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -11600,7 +11572,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -11690,7 +11661,6 @@
         </is>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -11837,7 +11807,6 @@
         <v/>
       </c>
     </row>
-    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>

--- a/LULU/model18_humanized.xlsx
+++ b/LULU/model18_humanized.xlsx
@@ -1225,9 +1225,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col hidden="1" outlineLevel="1" width="40" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -1756,9 +1756,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
-    <col hidden="1" outlineLevel="1" width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col hidden="1" outlineLevel="1" width="38" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
@@ -7415,9 +7415,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
-    <col hidden="1" outlineLevel="1" width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -7491,6 +7491,7 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -7697,6 +7698,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" hidden="1" outlineLevel="1">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -7876,9 +7878,10 @@
       </c>
     </row>
     <row r="21" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A21" s="23">
-        <f> Adjusted EBIT (Phase 1)</f>
-        <v/>
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>Adjusted EBIT (Phase 1)</t>
+        </is>
       </c>
       <c r="B21" s="17" t="n"/>
       <c r="C21" s="24" t="inlineStr">
@@ -8017,9 +8020,10 @@
       </c>
     </row>
     <row r="26" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A26" s="23">
-        <f> EBIT after lease &amp; capitalization (Phase 2)</f>
-        <v/>
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>EBIT after lease &amp; capitalization (Phase 2)</t>
+        </is>
       </c>
       <c r="B26" s="17" t="n"/>
       <c r="C26" s="24" t="inlineStr">
@@ -8313,9 +8317,10 @@
       </c>
     </row>
     <row r="35" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A35" s="23">
-        <f> EBIT after channel mix (Phase 3)</f>
-        <v/>
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>EBIT after channel mix (Phase 3)</t>
+        </is>
       </c>
       <c r="B35" s="17" t="n"/>
       <c r="C35" s="24" t="inlineStr">
@@ -8349,9 +8354,10 @@
       </c>
     </row>
     <row r="36" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A36" s="23">
-        <f> Normalized EBIT (tax base for NOPAT)</f>
-        <v/>
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>Normalized EBIT (tax base for NOPAT)</t>
+        </is>
       </c>
       <c r="B36" s="17" t="n"/>
       <c r="C36" s="24" t="inlineStr">
@@ -8524,6 +8530,7 @@
         <v/>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="61" t="inlineStr">
         <is>
@@ -8606,9 +8613,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col hidden="1" outlineLevel="1" width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col hidden="1" outlineLevel="1" width="36" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
@@ -8722,7 +8729,7 @@
       </c>
       <c r="D4" s="85" t="inlineStr">
         <is>
-          <t>'Revenue Drivers'!A1</t>
+          <t>Revenue Drivers tab</t>
         </is>
       </c>
     </row>
@@ -10945,9 +10952,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col hidden="1" outlineLevel="1" width="44" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>

--- a/LULU/model18_humanized.xlsx
+++ b/LULU/model18_humanized.xlsx
@@ -5386,9 +5386,8 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
-    <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="10" max="10"/>
-    <col hidden="1" outlineLevel="1" width="16" customWidth="1" min="11" max="11"/>
-    <col width="36" customWidth="1" min="12" max="12"/>
+    <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="10" max="11"/>
+    <col collapsed="1" width="36" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8496,7 +8495,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" ht="28" customHeight="1">
+    <row r="41" collapsed="1" ht="28" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
         <is>
           <t>NORMALIZED NOPAT</t>
@@ -9198,7 +9197,7 @@
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" collapsed="1">
       <c r="A19" s="52" t="inlineStr">
         <is>
           <t>Working capital schedule (driver-based) [click − to collapse detail]</t>

--- a/LULU/model18_humanized.xlsx
+++ b/LULU/model18_humanized.xlsx
@@ -1115,13 +1115,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B19"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1129,6 +1130,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -1143,6 +1145,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -1150,6 +1153,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -1171,6 +1175,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -1192,6 +1197,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17" ht="36" customHeight="1">
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -1199,12 +1205,9 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Built from scratch for the GIS IR selection assignment.</t>
-        </is>
-      </c>
+      <c r="B19" s="11" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1"/>
     <row r="21" ht="36" customHeight="1"/>
@@ -7490,7 +7493,6 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -7697,7 +7699,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" hidden="1" outlineLevel="1">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -8529,7 +8530,6 @@
         <v/>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="61" t="inlineStr">
         <is>

--- a/LULU/model18_humanized.xlsx
+++ b/LULU/model18_humanized.xlsx
@@ -1191,11 +1191,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>ASSUMPTIONS GUIDE (PDF — every tab)</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="n"/>
     </row>
     <row r="16"/>
     <row r="17" ht="36" customHeight="1">
@@ -1310,6 +1306,7 @@
         <v>0.3</v>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -1421,6 +1418,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
@@ -1638,6 +1636,7 @@
         <v/>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
@@ -1673,6 +1672,7 @@
         <v/>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -2237,6 +2237,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4239,6 +4240,7 @@
         <v/>
       </c>
     </row>
+    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4296,6 +4298,7 @@
         <v/>
       </c>
     </row>
+    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="inlineStr">
         <is>
@@ -4303,6 +4306,7 @@
         </is>
       </c>
     </row>
+    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -6098,6 +6102,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6577,6 +6582,7 @@
       </c>
       <c r="L34" s="19" t="n"/>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -6780,6 +6786,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7131,6 +7138,7 @@
       </c>
       <c r="L51" s="19" t="n"/>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -7493,6 +7501,7 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -7699,6 +7708,7 @@
         <v>4</v>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" hidden="1" outlineLevel="1">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -8530,6 +8540,7 @@
         <v/>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="61" t="inlineStr">
         <is>
@@ -8715,11 +8726,7 @@
       </c>
     </row>
     <row r="4" ht="36" customHeight="1">
-      <c r="A4" s="38" t="inlineStr">
-        <is>
-          <t>Full Assumptions Guide (PDF)</t>
-        </is>
-      </c>
+      <c r="A4" s="38" t="n"/>
       <c r="C4" s="85" t="inlineStr">
         <is>
           <t>NOPAT Bridge tab
@@ -9876,6 +9883,7 @@
         <v/>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
@@ -10118,6 +10126,8 @@
         <v/>
       </c>
     </row>
+    <row r="60"/>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -10136,6 +10146,7 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
@@ -10196,6 +10207,7 @@
         <v/>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -10280,6 +10292,7 @@
         <v/>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -10400,6 +10413,7 @@
         <v/>
       </c>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -10460,6 +10474,7 @@
         <v/>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="inlineStr">
         <is>
@@ -10543,6 +10558,7 @@
         <v/>
       </c>
     </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -10649,6 +10665,8 @@
       </c>
       <c r="D94" s="26" t="n"/>
     </row>
+    <row r="95"/>
+    <row r="96"/>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -10875,67 +10893,66 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId2"/>
     <hyperlink ref="C4" location="'NOPAT Bridge'!A1"/>
     <hyperlink ref="D4" location="'Revenue Drivers'!A1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId33"/>
     <hyperlink ref="C30" location="'Scenarios'!A105"/>
     <hyperlink ref="C31" location="'Scenarios'!A110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId35"/>
     <hyperlink ref="C33" location="'Scenarios'!A120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C50" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C51" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C55" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C57" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId44"/>
     <hyperlink ref="C82" location="'DCF'!E46"/>
     <hyperlink ref="M82" location="'Comps'!A45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C98" r:id="rId45"/>
     <hyperlink ref="L98" location="'Scenarios'!G10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C99" r:id="rId46"/>
     <hyperlink ref="L99" location="'WACC'!E41"/>
     <hyperlink ref="L100" location="'WACC'!E41"/>
     <hyperlink ref="L101" location="'WACC'!E41"/>
     <hyperlink ref="L102" location="'WACC'!E41"/>
     <hyperlink ref="L103" location="'WACC'!E41"/>
     <hyperlink ref="C104" location="'Scenarios'!G9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11121,6 +11138,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -11442,6 +11460,7 @@
         <v>407521</v>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
@@ -11528,6 +11547,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -11578,6 +11598,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -11667,6 +11688,7 @@
         </is>
       </c>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -11813,6 +11835,7 @@
         <v/>
       </c>
     </row>
+    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>

--- a/LULU/model18_humanized.xlsx
+++ b/LULU/model18_humanized.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="0.0x"/>
   </numFmts>
-  <fonts count="53">
+  <fonts count="54">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -346,6 +346,11 @@
       <sz val="11"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -405,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -749,6 +754,9 @@
     </xf>
     <xf numFmtId="165" fontId="52" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1115,14 +1123,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="B2:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1130,7 +1137,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -1145,7 +1151,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -1153,7 +1158,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -1175,7 +1179,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -1193,7 +1196,6 @@
     <row r="15">
       <c r="B15" s="5" t="n"/>
     </row>
-    <row r="16"/>
     <row r="17" ht="36" customHeight="1">
       <c r="B17" s="5" t="inlineStr">
         <is>
@@ -1201,7 +1203,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="11" t="n"/>
     </row>
@@ -1306,7 +1307,6 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -1418,7 +1418,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
@@ -1636,7 +1635,6 @@
         <v/>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
@@ -1672,7 +1670,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -2237,7 +2234,6 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4240,7 +4236,6 @@
         <v/>
       </c>
     </row>
-    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4298,7 +4293,6 @@
         <v/>
       </c>
     </row>
-    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="inlineStr">
         <is>
@@ -4306,7 +4300,6 @@
         </is>
       </c>
     </row>
-    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -6102,7 +6095,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6582,7 +6574,6 @@
       </c>
       <c r="L34" s="19" t="n"/>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -6786,7 +6777,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7138,7 +7128,6 @@
       </c>
       <c r="L51" s="19" t="n"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -7501,7 +7490,6 @@
     <row r="4">
       <c r="A4" s="26" t="n"/>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="52" t="inlineStr">
         <is>
@@ -7708,7 +7696,6 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14"/>
     <row r="15" hidden="1" outlineLevel="1">
       <c r="A15" s="73" t="inlineStr">
         <is>
@@ -8540,7 +8527,6 @@
         <v/>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="61" t="inlineStr">
         <is>
@@ -8561,18 +8547,14 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="26" t="inlineStr">
-        <is>
-          <t>Steps 1–4: DCF unchanged on FY26. Step 5 changes NOPAT only (tax). Step 6 changes FY26 EBIT (+ tariff).</t>
+      <c r="A44" s="126" t="inlineStr">
+        <is>
+          <t>FY26 EBIT adjusted for one-time tariff refund. Base/Bear/Bull paths link to normalized NOPAT using a flat operating tax rate.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="26" t="inlineStr">
-        <is>
-          <t>Scenarios base-case NOPAT (col G) links to NORMALIZED NOPAT above. Bear/bull apply the same t_operating to their EBIT paths.</t>
-        </is>
-      </c>
+      <c r="A45" s="26" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -8725,7 +8707,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="36" customHeight="1">
+    <row r="4" ht="15" customHeight="1">
       <c r="A4" s="38" t="n"/>
       <c r="C4" s="85" t="inlineStr">
         <is>
@@ -9883,7 +9865,6 @@
         <v/>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
@@ -10126,8 +10107,6 @@
         <v/>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -10146,7 +10125,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
@@ -10207,7 +10185,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -10292,7 +10269,6 @@
         <v/>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -10413,7 +10389,6 @@
         <v/>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -10474,7 +10449,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="inlineStr">
         <is>
@@ -10558,7 +10532,6 @@
         <v/>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -10665,8 +10638,6 @@
       </c>
       <c r="D94" s="26" t="n"/>
     </row>
-    <row r="95"/>
-    <row r="96"/>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -11138,7 +11109,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -11460,7 +11430,6 @@
         <v>407521</v>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
@@ -11547,7 +11516,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -11598,7 +11566,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -11688,7 +11655,6 @@
         </is>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -11835,7 +11801,6 @@
         <v/>
       </c>
     </row>
-    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>

--- a/LULU/model18_humanized.xlsx
+++ b/LULU/model18_humanized.xlsx
@@ -11,9 +11,8 @@
     <sheet name="WACC" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Scenarios" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Revenue Drivers" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="NOPAT Bridge" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="DCF" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Comps" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="DCF" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Comps" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1189,7 +1188,7 @@
     <row r="14">
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>WACC • Revenue Drivers • NOPAT Bridge • Scenarios • DCF • Comps / Football Field</t>
+          <t>WACC • Revenue Drivers • Scenarios • DCF • Comps / Football Field</t>
         </is>
       </c>
     </row>
@@ -2723,15 +2722,15 @@
         </is>
       </c>
       <c r="F50" s="42">
-        <f>F45*(1-'NOPAT Bridge'!F$39)</f>
+        <f>F45*(1-$G$11)</f>
         <v/>
       </c>
       <c r="G50" s="42">
-        <f>'NOPAT Bridge'!F41</f>
+        <f>G45*(1-$G$11)</f>
         <v/>
       </c>
       <c r="H50" s="42">
-        <f>H45*(1-'NOPAT Bridge'!F$39)</f>
+        <f>H45*(1-$G$11)</f>
         <v/>
       </c>
     </row>
@@ -2742,15 +2741,15 @@
         </is>
       </c>
       <c r="F51" s="42">
-        <f>F46*(1-'NOPAT Bridge'!G$39)</f>
+        <f>F46*(1-$G$11)</f>
         <v/>
       </c>
       <c r="G51" s="42">
-        <f>'NOPAT Bridge'!G41</f>
+        <f>G46*(1-$G$11)</f>
         <v/>
       </c>
       <c r="H51" s="42">
-        <f>H46*(1-'NOPAT Bridge'!G$39)</f>
+        <f>H46*(1-$G$11)</f>
         <v/>
       </c>
     </row>
@@ -2761,15 +2760,15 @@
         </is>
       </c>
       <c r="F52" s="42">
-        <f>F47*(1-'NOPAT Bridge'!H$39)</f>
+        <f>F47*(1-$G$11)</f>
         <v/>
       </c>
       <c r="G52" s="42">
-        <f>'NOPAT Bridge'!H41</f>
+        <f>G47*(1-$G$11)</f>
         <v/>
       </c>
       <c r="H52" s="42">
-        <f>H47*(1-'NOPAT Bridge'!H$39)</f>
+        <f>H47*(1-$G$11)</f>
         <v/>
       </c>
     </row>
@@ -2780,15 +2779,15 @@
         </is>
       </c>
       <c r="F53" s="42">
-        <f>F48*(1-'NOPAT Bridge'!I$39)</f>
+        <f>F48*(1-$G$11)</f>
         <v/>
       </c>
       <c r="G53" s="42">
-        <f>'NOPAT Bridge'!I41</f>
+        <f>G48*(1-$G$11)</f>
         <v/>
       </c>
       <c r="H53" s="42">
-        <f>H48*(1-'NOPAT Bridge'!I$39)</f>
+        <f>H48*(1-$G$11)</f>
         <v/>
       </c>
     </row>
@@ -2799,15 +2798,15 @@
         </is>
       </c>
       <c r="F54" s="42">
-        <f>F49*(1-'NOPAT Bridge'!J$39)</f>
+        <f>F49*(1-$G$11)</f>
         <v/>
       </c>
       <c r="G54" s="42">
-        <f>'NOPAT Bridge'!J41</f>
+        <f>G49*(1-$G$11)</f>
         <v/>
       </c>
       <c r="H54" s="42">
-        <f>H49*(1-'NOPAT Bridge'!J$39)</f>
+        <f>H49*(1-$G$11)</f>
         <v/>
       </c>
     </row>
@@ -7407,1197 +7406,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="inlineStr">
-        <is>
-          <t>NOPAT NORMALIZATION PIPELINE (BASE CASE)</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="n"/>
-      <c r="C1" s="13" t="n"/>
-      <c r="D1" s="13" t="n"/>
-      <c r="E1" s="13" t="n"/>
-      <c r="F1" s="13" t="n"/>
-      <c r="G1" s="13" t="n"/>
-      <c r="H1" s="13" t="n"/>
-      <c r="I1" s="13" t="n"/>
-      <c r="J1" s="13" t="n"/>
-    </row>
-    <row r="2">
-      <c r="B2" s="51" t="n"/>
-      <c r="C2" s="51" t="inlineStr">
-        <is>
-          <t>Source (click)</t>
-        </is>
-      </c>
-      <c r="D2" s="51" t="n"/>
-      <c r="E2" s="71" t="inlineStr">
-        <is>
-          <t>FY2025A</t>
-        </is>
-      </c>
-      <c r="F2" s="72" t="inlineStr">
-        <is>
-          <t>FY2026E</t>
-        </is>
-      </c>
-      <c r="G2" s="72" t="inlineStr">
-        <is>
-          <t>FY2027E</t>
-        </is>
-      </c>
-      <c r="H2" s="72" t="inlineStr">
-        <is>
-          <t>FY2028E</t>
-        </is>
-      </c>
-      <c r="I2" s="72" t="inlineStr">
-        <is>
-          <t>FY2029E</t>
-        </is>
-      </c>
-      <c r="J2" s="72" t="inlineStr">
-        <is>
-          <t>FY2030E</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="52" t="inlineStr">
-        <is>
-          <t>Reported EBIT → Normalized NOPAT (5-phase pipeline)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="26" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="52" t="inlineStr">
-        <is>
-          <t>Driver assumptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="16" t="inlineStr">
-        <is>
-          <t>Phase 1: Add back SBC? (0 = no — Convention A: expense stays in EBIT)</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="n"/>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>LULU CF statement (10-K): stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D7" s="19" t="n"/>
-      <c r="E7" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="40" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="26" t="inlineStr">
-        <is>
-          <t>Convention A: SBC is a real economic cost (captures shareholder dilution). Forecast NOPAT uses Scenarios EBIT with SBC expensed. DCF implied value uses basic shares (111.4M).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="70" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
-        <is>
-          <t>Phase 3: Store-channel EBIT margin %</t>
-        </is>
-      </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>FY2025 10-K: company-operated stores net revenue</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="n"/>
-      <c r="E9" s="20" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="F9" s="20" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="H9" s="20" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="I9" s="20" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="J9" s="20" t="n">
-        <v>0.186</v>
-      </c>
-    </row>
-    <row r="10" ht="70" customHeight="1">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>Phase 3: E-commerce EBIT margin %</t>
-        </is>
-      </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>FY2025 10-K: e-commerce net revenue</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="n"/>
-      <c r="E10" s="20" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="F10" s="20" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="I10" s="20" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="J10" s="20" t="n">
-        <v>0.236</v>
-      </c>
-    </row>
-    <row r="11" ht="70" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>Phase 3: Other-channels EBIT margin %</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>FY2025 10-K: other channels (residual)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="n"/>
-      <c r="E11" s="20" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="F11" s="20" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="G11" s="20" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="H11" s="20" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="I11" s="20" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="J11" s="20" t="n">
-        <v>0.091</v>
-      </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>Phase 4: Terminal marginal tax rate</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>Q2 FY2026 outlook: tax rate ≈ 30%</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="n"/>
-      <c r="E12" s="20" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F12" s="20" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G12" s="20" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
-        <is>
-          <t>Phase 2: R&amp;D / software amortization period (years)</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="24" t="inlineStr">
-        <is>
-          <t>NOPAT Bridge: capitalization convention</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="n"/>
-      <c r="E13" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="G13" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="I13" s="40" t="n">
-        <v>4</v>
-      </c>
-      <c r="J13" s="40" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" hidden="1" outlineLevel="1">
-      <c r="A15" s="73" t="inlineStr">
-        <is>
-          <t>Phase 1 — Operating normalization</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A16" s="16" t="inlineStr">
-        <is>
-          <t>Reported operating income (EBIT)</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: Income from operations</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="n"/>
-      <c r="E16" s="74" t="n">
-        <v>2210615</v>
-      </c>
-      <c r="F16" s="75">
-        <f>Scenarios!G45</f>
-        <v/>
-      </c>
-      <c r="G16" s="75">
-        <f>Scenarios!G46</f>
-        <v/>
-      </c>
-      <c r="H16" s="75">
-        <f>Scenarios!G47</f>
-        <v/>
-      </c>
-      <c r="I16" s="75">
-        <f>Scenarios!G48</f>
-        <v/>
-      </c>
-      <c r="J16" s="75">
-        <f>Scenarios!G49</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>+ Impairment / intangible amortization (add-back)</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: amortization of intangible assets</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="n"/>
-      <c r="E17" s="74" t="n">
-        <v>6961</v>
-      </c>
-      <c r="F17" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A18" s="16" t="inlineStr">
-        <is>
-          <t>+ Restructuring costs (add-back)</t>
-        </is>
-      </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: restructuring charges</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="n"/>
-      <c r="E18" s="74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A19" s="16" t="inlineStr">
-        <is>
-          <t>+ Legal / M&amp;A one-offs (add-back)</t>
-        </is>
-      </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: SG&amp;A one-offs</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="n"/>
-      <c r="E19" s="74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" hidden="1" outlineLevel="1" ht="42" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
-        <is>
-          <t>+ Stock-based compensation (add-back only if flag = 1)</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>LULU CF statement (10-K): stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="n"/>
-      <c r="E20" s="75">
-        <f>62203*$E$7</f>
-        <v/>
-      </c>
-      <c r="F20" s="75">
-        <f>Scenarios!G25/11102600*62203*$E$7</f>
-        <v/>
-      </c>
-      <c r="G20" s="75">
-        <f>Scenarios!G26/11102600*62203*$E$7</f>
-        <v/>
-      </c>
-      <c r="H20" s="75">
-        <f>Scenarios!G27/11102600*62203*$E$7</f>
-        <v/>
-      </c>
-      <c r="I20" s="75">
-        <f>Scenarios!G28/11102600*62203*$E$7</f>
-        <v/>
-      </c>
-      <c r="J20" s="75">
-        <f>Scenarios!G29/11102600*62203*$E$7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
-        <is>
-          <t>Adjusted EBIT (Phase 1)</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="24" t="inlineStr">
-        <is>
-          <t>NOPAT Bridge tab: Phase 1 subtotal</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="n"/>
-      <c r="F21" s="25">
-        <f>F16+F17+F18+F19+F20</f>
-        <v/>
-      </c>
-      <c r="G21" s="25">
-        <f>G16+G17+G18+G19+G20</f>
-        <v/>
-      </c>
-      <c r="H21" s="25">
-        <f>H16+H17+H18+H19+H20</f>
-        <v/>
-      </c>
-      <c r="I21" s="25">
-        <f>I16+I17+I18+I19+I20</f>
-        <v/>
-      </c>
-      <c r="J21" s="25">
-        <f>J16+J17+J18+J19+J20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" hidden="1" outlineLevel="1">
-      <c r="A22" s="73" t="inlineStr">
-        <is>
-          <t>Phase 2 — Lease &amp; capitalization (ASC 842 / IFRS 16)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" hidden="1" outlineLevel="1" ht="42" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
-        <is>
-          <t>+ Implied lease interest expense (reclass from rent)</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: interest on lease liabilities (supplemental)</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="n"/>
-      <c r="E23" s="74" t="n">
-        <v>1028</v>
-      </c>
-      <c r="F23" s="75">
-        <f>1028*(Scenarios!G25/11102600)</f>
-        <v/>
-      </c>
-      <c r="G23" s="75">
-        <f>1028*(Scenarios!G26/11102600)</f>
-        <v/>
-      </c>
-      <c r="H23" s="75">
-        <f>1028*(Scenarios!G27/11102600)</f>
-        <v/>
-      </c>
-      <c r="I23" s="75">
-        <f>1028*(Scenarios!G28/11102600)</f>
-        <v/>
-      </c>
-      <c r="J23" s="75">
-        <f>1028*(Scenarios!G29/11102600)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>+ Capitalize R&amp;D / software (current-year expense)</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: R&amp;D / software expense</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="n"/>
-      <c r="E24" s="74" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>− Amortization of prior capitalized intangibles</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: intangible amortization</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="n"/>
-      <c r="E25" s="74" t="n">
-        <v>6961</v>
-      </c>
-      <c r="F25" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="75" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="75" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A26" s="23" t="inlineStr">
-        <is>
-          <t>EBIT after lease &amp; capitalization (Phase 2)</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="24" t="inlineStr">
-        <is>
-          <t>NOPAT Bridge tab: Phase 2 subtotal</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="n"/>
-      <c r="F26" s="25">
-        <f>F21+F23+F24-F25</f>
-        <v/>
-      </c>
-      <c r="G26" s="25">
-        <f>G21+G23+G24-G25</f>
-        <v/>
-      </c>
-      <c r="H26" s="25">
-        <f>H21+H23+H24-H25</f>
-        <v/>
-      </c>
-      <c r="I26" s="25">
-        <f>I21+I23+I24-I25</f>
-        <v/>
-      </c>
-      <c r="J26" s="25">
-        <f>J21+J23+J24-J25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27" hidden="1" outlineLevel="1">
-      <c r="A27" s="73" t="inlineStr">
-        <is>
-          <t>Phase 3 — Segment / channel EBIT (driver-based)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>Store-channel revenue</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="n"/>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>Revenue Drivers tab: store-channel revenue</t>
-        </is>
-      </c>
-      <c r="D28" s="19" t="n"/>
-      <c r="E28" s="74" t="n">
-        <v>5049744</v>
-      </c>
-      <c r="F28" s="75">
-        <f>'Revenue Drivers'!F31</f>
-        <v/>
-      </c>
-      <c r="G28" s="75">
-        <f>'Revenue Drivers'!G31</f>
-        <v/>
-      </c>
-      <c r="H28" s="75">
-        <f>'Revenue Drivers'!H31</f>
-        <v/>
-      </c>
-      <c r="I28" s="75">
-        <f>'Revenue Drivers'!I31</f>
-        <v/>
-      </c>
-      <c r="J28" s="75">
-        <f>'Revenue Drivers'!J31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>E-commerce revenue</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="n"/>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>Revenue Drivers tab: e-commerce revenue</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="n"/>
-      <c r="E29" s="74" t="n">
-        <v>4918697</v>
-      </c>
-      <c r="F29" s="75">
-        <f>'Revenue Drivers'!F41</f>
-        <v/>
-      </c>
-      <c r="G29" s="75">
-        <f>'Revenue Drivers'!G41</f>
-        <v/>
-      </c>
-      <c r="H29" s="75">
-        <f>'Revenue Drivers'!H41</f>
-        <v/>
-      </c>
-      <c r="I29" s="75">
-        <f>'Revenue Drivers'!I41</f>
-        <v/>
-      </c>
-      <c r="J29" s="75">
-        <f>'Revenue Drivers'!J41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>Other channels revenue</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="n"/>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>Revenue Drivers tab: other channels revenue</t>
-        </is>
-      </c>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="74" t="n">
-        <v>1134159</v>
-      </c>
-      <c r="F30" s="75">
-        <f>'Revenue Drivers'!F45</f>
-        <v/>
-      </c>
-      <c r="G30" s="75">
-        <f>'Revenue Drivers'!G45</f>
-        <v/>
-      </c>
-      <c r="H30" s="75">
-        <f>'Revenue Drivers'!H45</f>
-        <v/>
-      </c>
-      <c r="I30" s="75">
-        <f>'Revenue Drivers'!I45</f>
-        <v/>
-      </c>
-      <c r="J30" s="75">
-        <f>'Revenue Drivers'!J45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31" hidden="1" outlineLevel="1" ht="70" customHeight="1">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>Store-channel EBIT (= Rev × store margin)</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="n"/>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>FY2025 10-K: company-operated stores net revenue</t>
-        </is>
-      </c>
-      <c r="D31" s="19" t="n"/>
-      <c r="E31" s="75" t="n">
-        <v>939252.384</v>
-      </c>
-      <c r="F31" s="75">
-        <f>F28*E$9</f>
-        <v/>
-      </c>
-      <c r="G31" s="75">
-        <f>G28*E$9</f>
-        <v/>
-      </c>
-      <c r="H31" s="75">
-        <f>H28*E$9</f>
-        <v/>
-      </c>
-      <c r="I31" s="75">
-        <f>I28*E$9</f>
-        <v/>
-      </c>
-      <c r="J31" s="75">
-        <f>J28*E$9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" hidden="1" outlineLevel="1" ht="70" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
-        <is>
-          <t>E-commerce EBIT (= Rev × e-comm margin)</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="n"/>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>FY2025 10-K: e-commerce net revenue</t>
-        </is>
-      </c>
-      <c r="D32" s="19" t="n"/>
-      <c r="E32" s="75" t="n">
-        <v>1160812.492</v>
-      </c>
-      <c r="F32" s="75">
-        <f>F29*E$10</f>
-        <v/>
-      </c>
-      <c r="G32" s="75">
-        <f>G29*E$10</f>
-        <v/>
-      </c>
-      <c r="H32" s="75">
-        <f>H29*E$10</f>
-        <v/>
-      </c>
-      <c r="I32" s="75">
-        <f>I29*E$10</f>
-        <v/>
-      </c>
-      <c r="J32" s="75">
-        <f>J29*E$10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" hidden="1" outlineLevel="1" ht="56" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>Other-channels EBIT (= Rev × other margin)</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="n"/>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>FY2025 10-K: other channels (residual)</t>
-        </is>
-      </c>
-      <c r="D33" s="19" t="n"/>
-      <c r="E33" s="75" t="n">
-        <v>103208.469</v>
-      </c>
-      <c r="F33" s="75">
-        <f>F30*E$11</f>
-        <v/>
-      </c>
-      <c r="G33" s="75">
-        <f>G30*E$11</f>
-        <v/>
-      </c>
-      <c r="H33" s="75">
-        <f>H30*E$11</f>
-        <v/>
-      </c>
-      <c r="I33" s="75">
-        <f>I30*E$11</f>
-        <v/>
-      </c>
-      <c r="J33" s="75">
-        <f>J30*E$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A34" s="23" t="inlineStr">
-        <is>
-          <t>Channel EBIT (sum of sector EBIT)</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="n"/>
-      <c r="C34" s="24" t="inlineStr">
-        <is>
-          <t>NOPAT Bridge tab: sector EBIT subtotal</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="n"/>
-      <c r="F34" s="70">
-        <f>F31+F32+F33+Scenarios!G7</f>
-        <v/>
-      </c>
-      <c r="G34" s="70">
-        <f>G31+G32+G33</f>
-        <v/>
-      </c>
-      <c r="H34" s="70">
-        <f>H31+H32+H33</f>
-        <v/>
-      </c>
-      <c r="I34" s="70">
-        <f>I31+I32+I33</f>
-        <v/>
-      </c>
-      <c r="J34" s="70">
-        <f>J31+J32+J33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A35" s="23" t="inlineStr">
-        <is>
-          <t>EBIT after channel mix (Phase 3)</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="n"/>
-      <c r="C35" s="24" t="inlineStr">
-        <is>
-          <t>NOPAT Bridge tab: Phase 3 subtotal</t>
-        </is>
-      </c>
-      <c r="D35" s="19" t="n"/>
-      <c r="E35" s="76" t="n">
-        <v>2203273.345</v>
-      </c>
-      <c r="F35" s="25">
-        <f>F34</f>
-        <v/>
-      </c>
-      <c r="G35" s="25">
-        <f>G34</f>
-        <v/>
-      </c>
-      <c r="H35" s="25">
-        <f>H34</f>
-        <v/>
-      </c>
-      <c r="I35" s="25">
-        <f>I34</f>
-        <v/>
-      </c>
-      <c r="J35" s="25">
-        <f>J34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>Normalized EBIT (tax base for NOPAT)</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="n"/>
-      <c r="C36" s="24" t="inlineStr">
-        <is>
-          <t>Scenarios tab: base-case EBIT (forecast)</t>
-        </is>
-      </c>
-      <c r="D36" s="19" t="n"/>
-      <c r="E36" s="25">
-        <f>E21+E23+E24-E25</f>
-        <v/>
-      </c>
-      <c r="F36" s="25">
-        <f>Scenarios!G45</f>
-        <v/>
-      </c>
-      <c r="G36" s="25">
-        <f>Scenarios!G46</f>
-        <v/>
-      </c>
-      <c r="H36" s="25">
-        <f>Scenarios!G47</f>
-        <v/>
-      </c>
-      <c r="I36" s="25">
-        <f>Scenarios!G48</f>
-        <v/>
-      </c>
-      <c r="J36" s="25">
-        <f>Scenarios!G49</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37" hidden="1" outlineLevel="1">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>Check vs Scenarios EBIT (base case)</t>
-        </is>
-      </c>
-      <c r="F37" s="75">
-        <f>F36-Scenarios!G45</f>
-        <v/>
-      </c>
-      <c r="G37" s="75">
-        <f>G36-Scenarios!G46</f>
-        <v/>
-      </c>
-      <c r="H37" s="75">
-        <f>H36-Scenarios!G47</f>
-        <v/>
-      </c>
-      <c r="I37" s="75">
-        <f>I36-Scenarios!G48</f>
-        <v/>
-      </c>
-      <c r="J37" s="75">
-        <f>J36-Scenarios!G49</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" hidden="1" outlineLevel="1">
-      <c r="A38" s="73" t="inlineStr">
-        <is>
-          <t>Phase 4 — Tax normalization to NOPAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" hidden="1" outlineLevel="1" ht="70" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>Operating effective tax rate (t_operating)</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="n"/>
-      <c r="C39" s="18" t="inlineStr">
-        <is>
-          <t>LULU FY2025 10-K: income tax &amp; interest expense</t>
-        </is>
-      </c>
-      <c r="D39" s="19" t="n"/>
-      <c r="E39" s="77" t="n">
-        <v>0.2946847649213503</v>
-      </c>
-      <c r="F39" s="32">
-        <f>0.29468476492135026+(F$12-0.29468476492135026)*1/5</f>
-        <v/>
-      </c>
-      <c r="G39" s="32">
-        <f>0.29468476492135026+(G$12-0.29468476492135026)*2/5</f>
-        <v/>
-      </c>
-      <c r="H39" s="32">
-        <f>0.29468476492135026+(H$12-0.29468476492135026)*3/5</f>
-        <v/>
-      </c>
-      <c r="I39" s="32">
-        <f>0.29468476492135026+(I$12-0.29468476492135026)*4/5</f>
-        <v/>
-      </c>
-      <c r="J39" s="32">
-        <f>0.29468476492135026+(J$12-0.29468476492135026)*5/5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40" hidden="1" outlineLevel="1" ht="28" customHeight="1">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>Unlevered tax on normalized EBIT</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="n"/>
-      <c r="C40" s="24" t="inlineStr">
-        <is>
-          <t>NOPAT Bridge tab: unlevered tax expense</t>
-        </is>
-      </c>
-      <c r="D40" s="19" t="n"/>
-      <c r="F40" s="75">
-        <f>F36*F39</f>
-        <v/>
-      </c>
-      <c r="G40" s="75">
-        <f>G36*G39</f>
-        <v/>
-      </c>
-      <c r="H40" s="75">
-        <f>H36*H39</f>
-        <v/>
-      </c>
-      <c r="I40" s="75">
-        <f>I36*I39</f>
-        <v/>
-      </c>
-      <c r="J40" s="75">
-        <f>J36*J39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" collapsed="1" ht="28" customHeight="1">
-      <c r="A41" s="23" t="inlineStr">
-        <is>
-          <t>NORMALIZED NOPAT</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="n"/>
-      <c r="C41" s="24" t="inlineStr">
-        <is>
-          <t>NOPAT Bridge tab: normalized NOPAT</t>
-        </is>
-      </c>
-      <c r="D41" s="19" t="n"/>
-      <c r="F41" s="25">
-        <f>F36-F40</f>
-        <v/>
-      </c>
-      <c r="G41" s="25">
-        <f>G36-G40</f>
-        <v/>
-      </c>
-      <c r="H41" s="25">
-        <f>H36-H40</f>
-        <v/>
-      </c>
-      <c r="I41" s="25">
-        <f>I36-I40</f>
-        <v/>
-      </c>
-      <c r="J41" s="25">
-        <f>J36-J40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="61" t="inlineStr">
-        <is>
-          <t>6. Tariff refund (Scenarios)</t>
-        </is>
-      </c>
-      <c r="B43" s="79" t="n"/>
-      <c r="C43" s="79" t="inlineStr">
-        <is>
-          <t>EBIT = Rev × 13.2% only (no refund).</t>
-        </is>
-      </c>
-      <c r="D43" s="79" t="n"/>
-      <c r="F43" s="80" t="inlineStr">
-        <is>
-          <t>Scenarios EBIT (FY26)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="126" t="inlineStr">
-        <is>
-          <t>FY26 EBIT adjusted for one-time tariff refund. Base/Bear/Bull paths link to normalized NOPAT using a flat operating tax rate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="26" t="n"/>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId20"/>
-    <hyperlink ref="C28" location="'Revenue Drivers'!B31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId21"/>
-    <hyperlink ref="C29" location="'Revenue Drivers'!B41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId22"/>
-    <hyperlink ref="C30" location="'Revenue Drivers'!B45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId29"/>
-  </hyperlinks>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
     <outlinePr applyStyles="1" summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -9000,27 +7808,27 @@
     <row r="13">
       <c r="A13" s="16" t="inlineStr">
         <is>
-          <t>Less: unlevered tax (t_operating from NOPAT Bridge)</t>
+          <t>Less: unlevered tax (cash tax rate)</t>
         </is>
       </c>
       <c r="F13" s="75">
-        <f>-'NOPAT Bridge'!F40</f>
+        <f>-F11*Scenarios!$G$11</f>
         <v/>
       </c>
       <c r="G13" s="75">
-        <f>-'NOPAT Bridge'!G40</f>
+        <f>-G11*Scenarios!$G$11</f>
         <v/>
       </c>
       <c r="H13" s="75">
-        <f>-'NOPAT Bridge'!H40</f>
+        <f>-H11*Scenarios!$G$11</f>
         <v/>
       </c>
       <c r="I13" s="75">
-        <f>-'NOPAT Bridge'!I40</f>
+        <f>-I11*Scenarios!$G$11</f>
         <v/>
       </c>
       <c r="J13" s="75">
-        <f>-'NOPAT Bridge'!J40</f>
+        <f>-J11*Scenarios!$G$11</f>
         <v/>
       </c>
     </row>
@@ -10399,23 +9207,23 @@
         <v>1579183</v>
       </c>
       <c r="F77" s="75">
-        <f>('NOPAT Bridge'!F36-'NOPAT Bridge'!F23)*(1-'NOPAT Bridge'!F$39)</f>
+        <f>F14</f>
         <v/>
       </c>
       <c r="G77" s="75">
-        <f>('NOPAT Bridge'!G36-'NOPAT Bridge'!G23)*(1-'NOPAT Bridge'!G$39)</f>
+        <f>G14</f>
         <v/>
       </c>
       <c r="H77" s="75">
-        <f>('NOPAT Bridge'!H36-'NOPAT Bridge'!H23)*(1-'NOPAT Bridge'!H$39)</f>
+        <f>H14</f>
         <v/>
       </c>
       <c r="I77" s="75">
-        <f>('NOPAT Bridge'!I36-'NOPAT Bridge'!I23)*(1-'NOPAT Bridge'!I$39)</f>
+        <f>I14</f>
         <v/>
       </c>
       <c r="J77" s="75">
-        <f>('NOPAT Bridge'!J36-'NOPAT Bridge'!J23)*(1-'NOPAT Bridge'!J$39)</f>
+        <f>J14</f>
         <v/>
       </c>
     </row>
@@ -10929,7 +9737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1"/>

--- a/LULU/model18_humanized.xlsx
+++ b/LULU/model18_humanized.xlsx
@@ -1196,11 +1196,7 @@
       <c r="B15" s="5" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1">
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>SOURCES</t>
-        </is>
-      </c>
+      <c r="B17" s="5" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="11" t="n"/>

--- a/LULU/model18_humanized.xlsx
+++ b/LULU/model18_humanized.xlsx
@@ -29,7 +29,7 @@
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="0.0x"/>
   </numFmts>
-  <fonts count="54">
+  <fonts count="56">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -350,6 +350,16 @@
       <i val="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="000563C1"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -409,7 +419,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -757,6 +767,14 @@
     <xf numFmtId="0" fontId="53" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1747,7 +1765,7 @@
     <outlinePr applyStyles="1" summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H193"/>
+  <dimension ref="A1:H198"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2229,6 +2247,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4231,6 +4250,7 @@
         <v/>
       </c>
     </row>
+    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4288,6 +4308,7 @@
         <v/>
       </c>
     </row>
+    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="inlineStr">
         <is>
@@ -4295,6 +4316,7 @@
         </is>
       </c>
     </row>
+    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -5337,6 +5359,20 @@
         <is>
           <t>memo: pitch deck pulls cols G (base) &amp; H (bull) from this block via pitch_values.py</t>
         </is>
+      </c>
+    </row>
+    <row r="194"/>
+    <row r="195"/>
+    <row r="196"/>
+    <row r="197"/>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>FY25 net revenue ($000)</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>11102600</v>
       </c>
     </row>
   </sheetData>
@@ -5381,7 +5417,8 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="40" customWidth="1" min="9" max="9"/>
-    <col hidden="1" outlineLevel="1" width="28" customWidth="1" min="10" max="11"/>
+    <col width="28" customWidth="1" min="10" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col collapsed="1" width="36" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -5477,7 +5514,11 @@
           <t>Equation</t>
         </is>
       </c>
-      <c r="J5" s="56" t="n"/>
+      <c r="J5" s="127" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
       <c r="K5" s="56" t="inlineStr">
         <is>
           <t>Source</t>
@@ -5524,7 +5565,11 @@
           <t>prior-year ending stores. Same count, new column; that's where the year starts.</t>
         </is>
       </c>
-      <c r="J6" s="17" t="n"/>
+      <c r="J6" s="128" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: beginning-stores formula</t>
+        </is>
+      </c>
       <c r="K6" s="24" t="inlineStr">
         <is>
           <t>Revenue Drivers: beginning-stores formula</t>
@@ -5557,7 +5602,11 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="J7" s="17" t="n"/>
+      <c r="J7" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: store count &amp; expansion</t>
+        </is>
+      </c>
       <c r="K7" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: store count &amp; expansion</t>
@@ -5591,7 +5640,11 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="J8" s="17" t="n"/>
+      <c r="J8" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: lease renewal / fleet</t>
+        </is>
+      </c>
       <c r="K8" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: lease renewal / fleet</t>
@@ -5638,7 +5691,11 @@
           <t>beginning stores + openings − closures. Roll-forward; nothing fancy, just how many doors you end with.</t>
         </is>
       </c>
-      <c r="J9" s="17" t="n"/>
+      <c r="J9" s="128" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: ending-stores formula</t>
+        </is>
+      </c>
       <c r="K9" s="24" t="inlineStr">
         <is>
           <t>Revenue Drivers: ending-stores formula</t>
@@ -5684,7 +5741,11 @@
           <t>prior-year ending stores. Same count, new column; that's where the year starts.</t>
         </is>
       </c>
-      <c r="J10" s="17" t="n"/>
+      <c r="J10" s="128" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: beginning-stores formula</t>
+        </is>
+      </c>
       <c r="K10" s="24" t="inlineStr">
         <is>
           <t>Revenue Drivers: beginning-stores formula</t>
@@ -5717,7 +5778,11 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="J11" s="17" t="n"/>
+      <c r="J11" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: store count &amp; expansion</t>
+        </is>
+      </c>
       <c r="K11" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: store count &amp; expansion</t>
@@ -5751,7 +5816,11 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="J12" s="17" t="n"/>
+      <c r="J12" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: lease renewal / fleet</t>
+        </is>
+      </c>
       <c r="K12" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: lease renewal / fleet</t>
@@ -5798,7 +5867,11 @@
           <t>beginning stores + openings − closures. Roll-forward; nothing fancy, just how many doors you end with.</t>
         </is>
       </c>
-      <c r="J13" s="17" t="n"/>
+      <c r="J13" s="128" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: ending-stores formula</t>
+        </is>
+      </c>
       <c r="K13" s="24" t="inlineStr">
         <is>
           <t>Revenue Drivers: ending-stores formula</t>
@@ -5844,7 +5917,11 @@
           <t>prior-year ending stores. Same count, new column; that's where the year starts.</t>
         </is>
       </c>
-      <c r="J14" s="17" t="n"/>
+      <c r="J14" s="128" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: beginning-stores formula</t>
+        </is>
+      </c>
       <c r="K14" s="24" t="inlineStr">
         <is>
           <t>Revenue Drivers: beginning-stores formula</t>
@@ -5877,7 +5954,11 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="J15" s="17" t="n"/>
+      <c r="J15" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: store count &amp; expansion</t>
+        </is>
+      </c>
       <c r="K15" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: store count &amp; expansion</t>
@@ -5911,7 +5992,11 @@
           <t>stores</t>
         </is>
       </c>
-      <c r="J16" s="17" t="n"/>
+      <c r="J16" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: lease renewal / fleet</t>
+        </is>
+      </c>
       <c r="K16" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: lease renewal / fleet</t>
@@ -5958,7 +6043,11 @@
           <t>beginning stores + openings − closures. Roll-forward; nothing fancy, just how many doors you end with.</t>
         </is>
       </c>
-      <c r="J17" s="17" t="n"/>
+      <c r="J17" s="128" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: ending-stores formula</t>
+        </is>
+      </c>
       <c r="K17" s="24" t="inlineStr">
         <is>
           <t>Revenue Drivers: ending-stores formula</t>
@@ -5999,7 +6088,11 @@
           <t>Americas ending + China ending + RoW ending. Should foot to total company-operated stores.</t>
         </is>
       </c>
-      <c r="J18" s="17" t="n"/>
+      <c r="J18" s="128" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: total-stores formula</t>
+        </is>
+      </c>
       <c r="K18" s="24" t="inlineStr">
         <is>
           <t>Revenue Drivers: total-stores formula</t>
@@ -6035,7 +6128,11 @@
           <t>sq ft</t>
         </is>
       </c>
-      <c r="J19" s="17" t="n"/>
+      <c r="J19" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: sales per square foot</t>
+        </is>
+      </c>
       <c r="K19" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: sales per square foot</t>
@@ -6083,13 +6180,18 @@
           <t>total ending stores × avg sq ft per store. Fleet size in square feet for the productivity lines.</t>
         </is>
       </c>
-      <c r="J20" s="17" t="n"/>
+      <c r="J20" s="129" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: total-sqft formula</t>
+        </is>
+      </c>
       <c r="K20" s="24" t="inlineStr">
         <is>
           <t>Revenue Drivers: total-sqft formula</t>
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6143,7 +6245,11 @@
           <t>Equation</t>
         </is>
       </c>
-      <c r="J23" s="56" t="n"/>
+      <c r="J23" s="130" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
       <c r="K23" s="56" t="inlineStr">
         <is>
           <t>Source</t>
@@ -6180,7 +6286,11 @@
           <t>$/sq ft</t>
         </is>
       </c>
-      <c r="J24" s="17" t="n"/>
+      <c r="J24" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: comparable sales &amp; SPSF</t>
+        </is>
+      </c>
       <c r="K24" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: comparable sales &amp; SPSF</t>
@@ -6217,7 +6327,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="J25" s="17" t="n"/>
+      <c r="J25" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: Americas comparable sales</t>
+        </is>
+      </c>
       <c r="K25" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: Americas comparable sales</t>
@@ -6254,7 +6368,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="J26" s="17" t="n"/>
+      <c r="J26" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: China Mainland comparable sales</t>
+        </is>
+      </c>
       <c r="K26" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: China Mainland comparable sales</t>
@@ -6291,7 +6409,11 @@
           <t>%</t>
         </is>
       </c>
-      <c r="J27" s="17" t="n"/>
+      <c r="J27" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: Rest of World comparable sales</t>
+        </is>
+      </c>
       <c r="K27" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: Rest of World comparable sales</t>
@@ -6338,7 +6460,11 @@
           <t>prior column's total store-channel revenue. Base you're applying comps to; not new-store contribution.</t>
         </is>
       </c>
-      <c r="J28" s="17" t="n"/>
+      <c r="J28" s="128" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: prior store-rev formula</t>
+        </is>
+      </c>
       <c r="K28" s="24" t="inlineStr">
         <is>
           <t>Revenue Drivers: prior store-rev formula</t>
@@ -6379,7 +6505,11 @@
           <t>prior store rev×(71%×(1+Am comp)+16%×(1+China)+13%×(1+RoW)). Existing base only; new stores are on the next row.</t>
         </is>
       </c>
-      <c r="J29" s="17" t="n"/>
+      <c r="J29" s="128" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: comp-store formula</t>
+        </is>
+      </c>
       <c r="K29" s="24" t="inlineStr">
         <is>
           <t>Revenue Drivers: comp-store formula</t>
@@ -6420,7 +6550,11 @@
           <t>(open−close each geo)×sq ft×$/sq ft → raw annual $. /1000 flips that to $000 (this whole tab is thousands). ×0.55 = year-one haircut; new boxes don't run at full SPSF yet. FY27 ex: (D7−D8+D11−D12+D15−D16)×D19×D24/1000×0.55.</t>
         </is>
       </c>
-      <c r="J30" s="17" t="n"/>
+      <c r="J30" s="129" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: net-new-store formula</t>
+        </is>
+      </c>
       <c r="K30" s="24" t="inlineStr">
         <is>
           <t>Revenue Drivers: net-new-store formula</t>
@@ -6461,7 +6595,11 @@
           <t>comparable store revenue + net new store revenue. Full brick-and-mortar channel for the year.</t>
         </is>
       </c>
-      <c r="J31" s="17" t="n"/>
+      <c r="J31" s="128" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: store-channel formula</t>
+        </is>
+      </c>
       <c r="K31" s="24" t="inlineStr">
         <is>
           <t>Revenue Drivers: store-channel formula</t>
@@ -6497,7 +6635,11 @@
           <t>M visits</t>
         </is>
       </c>
-      <c r="J32" s="17" t="n"/>
+      <c r="J32" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: store traffic commentary</t>
+        </is>
+      </c>
       <c r="K32" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: store traffic commentary</t>
@@ -6529,7 +6671,11 @@
       <c r="G33" s="64" t="n">
         <v>0.29</v>
       </c>
-      <c r="J33" s="17" t="n"/>
+      <c r="J33" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: conversion rate commentary</t>
+        </is>
+      </c>
       <c r="K33" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: conversion rate commentary</t>
@@ -6561,7 +6707,11 @@
       <c r="G34" s="67" t="n">
         <v>122</v>
       </c>
-      <c r="J34" s="17" t="n"/>
+      <c r="J34" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: average order value commentary</t>
+        </is>
+      </c>
       <c r="K34" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: average order value commentary</t>
@@ -6569,6 +6719,7 @@
       </c>
       <c r="L34" s="19" t="n"/>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -6622,7 +6773,11 @@
           <t>Equation</t>
         </is>
       </c>
-      <c r="J37" s="56" t="n"/>
+      <c r="J37" s="130" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
       <c r="K37" s="56" t="inlineStr">
         <is>
           <t>Source</t>
@@ -6659,7 +6814,11 @@
           <t>M</t>
         </is>
       </c>
-      <c r="J38" s="17" t="n"/>
+      <c r="J38" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: e-commerce revenue</t>
+        </is>
+      </c>
       <c r="K38" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: e-commerce revenue</t>
@@ -6691,7 +6850,11 @@
       <c r="G39" s="64" t="n">
         <v>0.036</v>
       </c>
-      <c r="J39" s="17" t="n"/>
+      <c r="J39" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: digital / traffic commentary</t>
+        </is>
+      </c>
       <c r="K39" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: digital / traffic commentary</t>
@@ -6723,7 +6886,11 @@
       <c r="G40" s="67" t="n">
         <v>315</v>
       </c>
-      <c r="J40" s="17" t="n"/>
+      <c r="J40" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: e-commerce revenue</t>
+        </is>
+      </c>
       <c r="K40" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: e-commerce revenue</t>
@@ -6765,13 +6932,18 @@
           <t>sessions×1,000,000×conversion×AOV/1000 → e-comm $000. ×1M 'cause sessions are millions; /1000 matches tab units.</t>
         </is>
       </c>
-      <c r="J41" s="17" t="n"/>
+      <c r="J41" s="128" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: e-comm formula</t>
+        </is>
+      </c>
       <c r="K41" s="24" t="inlineStr">
         <is>
           <t>Revenue Drivers: e-comm formula</t>
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -6825,7 +6997,11 @@
           <t>Equation</t>
         </is>
       </c>
-      <c r="J44" s="56" t="n"/>
+      <c r="J44" s="130" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
       <c r="K44" s="56" t="inlineStr">
         <is>
           <t>Source</t>
@@ -6872,7 +7048,11 @@
           <t>prior other-channel rev × (1 + growth %). Wholesale/license/outlets; grown off last year.</t>
         </is>
       </c>
-      <c r="J45" s="17" t="n"/>
+      <c r="J45" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: channel revenue table</t>
+        </is>
+      </c>
       <c r="K45" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: channel revenue table</t>
@@ -6921,7 +7101,11 @@
 FY26E plugged: B46 × (C31+C41+C45) ÷ (B31+B41+B45)</t>
         </is>
       </c>
-      <c r="J46" s="17" t="n"/>
+      <c r="J46" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: segmented net revenue</t>
+        </is>
+      </c>
       <c r="K46" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: segmented net revenue</t>
@@ -6970,7 +7154,11 @@
 FY26E plugged: B47 × (C31+C41+C45) ÷ (B31+B41+B45)</t>
         </is>
       </c>
-      <c r="J47" s="17" t="n"/>
+      <c r="J47" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: segmented net revenue</t>
+        </is>
+      </c>
       <c r="K47" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: segmented net revenue</t>
@@ -7019,7 +7207,11 @@
 FY26E plugged: B48 × (C31+C41+C45) ÷ (B31+B41+B45)</t>
         </is>
       </c>
-      <c r="J48" s="17" t="n"/>
+      <c r="J48" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: segmented net revenue</t>
+        </is>
+      </c>
       <c r="K48" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: segmented net revenue</t>
@@ -7051,7 +7243,11 @@
       <c r="G49" s="64" t="n">
         <v>0.6</v>
       </c>
-      <c r="J49" s="17" t="n"/>
+      <c r="J49" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: product category mix</t>
+        </is>
+      </c>
       <c r="K49" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: product category mix</t>
@@ -7083,7 +7279,11 @@
       <c r="G50" s="64" t="n">
         <v>0.27</v>
       </c>
-      <c r="J50" s="17" t="n"/>
+      <c r="J50" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: product category mix</t>
+        </is>
+      </c>
       <c r="K50" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: product category mix</t>
@@ -7115,7 +7315,11 @@
       <c r="G51" s="64" t="n">
         <v>0.13</v>
       </c>
-      <c r="J51" s="17" t="n"/>
+      <c r="J51" s="128" t="inlineStr">
+        <is>
+          <t>FY2025 10-K: product category mix</t>
+        </is>
+      </c>
       <c r="K51" s="18" t="inlineStr">
         <is>
           <t>FY2025 10-K: product category mix</t>
@@ -7123,6 +7327,7 @@
       </c>
       <c r="L51" s="19" t="n"/>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
@@ -7176,7 +7381,11 @@
           <t>Equation</t>
         </is>
       </c>
-      <c r="J54" s="56" t="n"/>
+      <c r="J54" s="130" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
       <c r="K54" s="56" t="inlineStr">
         <is>
           <t>Source</t>
@@ -7218,7 +7427,11 @@
           <t>store channel + e-commerce + other. Bottom-up top line before you reconcile to Scenarios.</t>
         </is>
       </c>
-      <c r="J55" s="17" t="n"/>
+      <c r="J55" s="128" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: total-rev formula</t>
+        </is>
+      </c>
       <c r="K55" s="24" t="inlineStr">
         <is>
           <t>Revenue Drivers: total-rev formula</t>
@@ -7259,7 +7472,11 @@
           <t>Scenarios! base-case revenue. DCF still runs off this path; not the driver total.</t>
         </is>
       </c>
-      <c r="J56" s="17" t="n"/>
+      <c r="J56" s="128" t="inlineStr">
+        <is>
+          <t>Scenarios tab: base revenue</t>
+        </is>
+      </c>
       <c r="K56" s="18" t="inlineStr">
         <is>
           <t>Scenarios tab: base revenue</t>
@@ -7301,7 +7518,11 @@
           <t>bottom-up total − Scenarios revenue. Positive = drivers above Scenarios; negative = below.</t>
         </is>
       </c>
-      <c r="J57" s="17" t="n"/>
+      <c r="J57" s="129" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: variance formula</t>
+        </is>
+      </c>
       <c r="K57" s="24" t="inlineStr">
         <is>
           <t>Revenue Drivers: variance formula</t>
@@ -7343,7 +7564,11 @@
           <t>variance ÷ Scenarios revenue. Quick % read on how far the driver build is from the valuation path.</t>
         </is>
       </c>
-      <c r="J58" s="17" t="n"/>
+      <c r="J58" s="129" t="inlineStr">
+        <is>
+          <t>Revenue Drivers: variance % formula</t>
+        </is>
+      </c>
       <c r="K58" s="24" t="inlineStr">
         <is>
           <t>Revenue Drivers: variance % formula</t>
@@ -7359,40 +7584,77 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J8" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J17" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J25" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K25" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K26" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J28" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J29" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J31" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J32" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K32" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J33" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K33" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J34" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K34" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J38" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K38" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J39" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K39" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J40" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K40" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J41" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J45" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K45" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J46" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K46" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J47" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K47" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J48" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K48" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J49" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K49" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J50" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K50" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J51" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K51" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J55" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId70"/>
+    <hyperlink ref="J56" location="'Scenarios'!G25"/>
     <hyperlink ref="K56" location="'Scenarios'!G25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7997,7 +8259,7 @@
         </is>
       </c>
     </row>
-    <row r="20" hidden="1" outlineLevel="1" ht="150" customHeight="1">
+    <row r="20" outlineLevel="1" ht="150" customHeight="1">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t>DSO (days) — flat vs FY25</t>
@@ -8038,7 +8300,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" hidden="1" outlineLevel="1" ht="98" customHeight="1">
+    <row r="21" outlineLevel="1" ht="98" customHeight="1">
       <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Accounts receivable, net</t>
@@ -8079,7 +8341,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" hidden="1" outlineLevel="1" ht="150" customHeight="1">
+    <row r="22" outlineLevel="1" ht="150" customHeight="1">
       <c r="A22" s="16" t="inlineStr">
         <is>
           <t>DIO (days) — FY25 anchor, −1 day/yr</t>
@@ -8121,7 +8383,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" hidden="1" outlineLevel="1" ht="112" customHeight="1">
+    <row r="23" outlineLevel="1" ht="112" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Inventories</t>
@@ -8162,7 +8424,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" hidden="1" outlineLevel="1" ht="84" customHeight="1">
+    <row r="24" outlineLevel="1" ht="84" customHeight="1">
       <c r="A24" s="16" t="inlineStr">
         <is>
           <t>DPO (days) — flat vs FY25</t>
@@ -8203,7 +8465,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" hidden="1" outlineLevel="1" ht="84" customHeight="1">
+    <row r="25" outlineLevel="1" ht="84" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Accounts payable</t>
@@ -8244,7 +8506,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" hidden="1" outlineLevel="1" ht="84" customHeight="1">
+    <row r="26" outlineLevel="1" ht="84" customHeight="1">
       <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Prepaid expenses (% of revenue)</t>
@@ -8281,7 +8543,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" hidden="1" outlineLevel="1" ht="84" customHeight="1">
+    <row r="27" outlineLevel="1" ht="84" customHeight="1">
       <c r="A27" s="16" t="inlineStr">
         <is>
           <t>Prepaid expenses (other current assets)</t>
@@ -8322,7 +8584,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" hidden="1" outlineLevel="1" ht="84" customHeight="1">
+    <row r="28" outlineLevel="1" ht="84" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Accrued liabilities (% of revenue)</t>
@@ -8359,7 +8621,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" hidden="1" outlineLevel="1" ht="84" customHeight="1">
+    <row r="29" outlineLevel="1" ht="84" customHeight="1">
       <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Accrued liabilities and other</t>
@@ -8400,7 +8662,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="30" outlineLevel="1" ht="42" customHeight="1">
       <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Current operating assets (AR + inv + prepaids)</t>
@@ -8438,7 +8700,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="31" outlineLevel="1" ht="42" customHeight="1">
       <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Current operating liabilities (AP + accruals)</t>
@@ -8476,7 +8738,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" hidden="1" outlineLevel="1" ht="42" customHeight="1">
+    <row r="32" outlineLevel="1" ht="42" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
         <is>
           <t>Net working capital</t>

--- a/LULU/model18_humanized.xlsx
+++ b/LULU/model18_humanized.xlsx
@@ -21,13 +21,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="$#,##0.00"/>
     <numFmt numFmtId="166" formatCode="#,##0;(#,##0)"/>
     <numFmt numFmtId="167" formatCode="#,##0.0"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="0.0x"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
   <fonts count="56">
     <font>
@@ -419,7 +420,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -775,6 +776,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1140,13 +1147,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B19"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1154,6 +1162,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -1168,6 +1177,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -1175,6 +1185,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -1196,6 +1207,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -1213,9 +1225,11 @@
     <row r="15">
       <c r="B15" s="5" t="n"/>
     </row>
+    <row r="16"/>
     <row r="17" ht="36" customHeight="1">
       <c r="B17" s="5" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="B19" s="11" t="n"/>
     </row>
@@ -1320,6 +1334,7 @@
         <v>0.3</v>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -1431,6 +1446,7 @@
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
@@ -1648,6 +1664,7 @@
         <v/>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
@@ -1683,6 +1700,7 @@
         <v/>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -2090,14 +2108,17 @@
         </is>
       </c>
       <c r="D15" s="19" t="n"/>
-      <c r="F15" s="39" t="n">
-        <v>6.267883648875038</v>
-      </c>
-      <c r="G15" s="39" t="n">
-        <v>6.267883648875038</v>
-      </c>
-      <c r="H15" s="39" t="n">
-        <v>6.267883648875038</v>
+      <c r="F15" s="131">
+        <f>(DCF!$E$21/DCF!$E$5)*365</f>
+        <v/>
+      </c>
+      <c r="G15" s="131">
+        <f>(DCF!$E$21/DCF!$E$5)*365</f>
+        <v/>
+      </c>
+      <c r="H15" s="131">
+        <f>(DCF!$E$21/DCF!$E$5)*365</f>
+        <v/>
       </c>
     </row>
     <row r="16" ht="140" customHeight="1">
@@ -2113,14 +2134,17 @@
         </is>
       </c>
       <c r="D16" s="19" t="n"/>
-      <c r="F16" s="39" t="n">
-        <v>128.8324100108167</v>
-      </c>
-      <c r="G16" s="39" t="n">
-        <v>128.8324100108167</v>
-      </c>
-      <c r="H16" s="39" t="n">
-        <v>128.8324100108167</v>
+      <c r="F16" s="131">
+        <f>(DCF!$E$23/DCF!$E$8)*365</f>
+        <v/>
+      </c>
+      <c r="G16" s="131">
+        <f>(DCF!$E$23/DCF!$E$8)*365</f>
+        <v/>
+      </c>
+      <c r="H16" s="131">
+        <f>(DCF!$E$23/DCF!$E$8)*365</f>
+        <v/>
       </c>
     </row>
     <row r="17" ht="70" customHeight="1">
@@ -2159,14 +2183,17 @@
         </is>
       </c>
       <c r="D18" s="19" t="n"/>
-      <c r="F18" s="39" t="n">
-        <v>25.10521290169407</v>
-      </c>
-      <c r="G18" s="39" t="n">
-        <v>25.10521290169407</v>
-      </c>
-      <c r="H18" s="39" t="n">
-        <v>25.10521290169407</v>
+      <c r="F18" s="131">
+        <f>(DCF!$E$25/DCF!$E$8)*365</f>
+        <v/>
+      </c>
+      <c r="G18" s="131">
+        <f>(DCF!$E$25/DCF!$E$8)*365</f>
+        <v/>
+      </c>
+      <c r="H18" s="131">
+        <f>(DCF!$E$25/DCF!$E$8)*365</f>
+        <v/>
       </c>
     </row>
     <row r="19" ht="84" customHeight="1">
@@ -2182,14 +2209,17 @@
         </is>
       </c>
       <c r="D19" s="19" t="n"/>
-      <c r="F19" s="20" t="n">
-        <v>0.05080692810692991</v>
-      </c>
-      <c r="G19" s="20" t="n">
-        <v>0.05080692810692991</v>
-      </c>
-      <c r="H19" s="20" t="n">
-        <v>0.05080692810692991</v>
+      <c r="F19" s="20">
+        <f>DCF!$E$27/DCF!$E$5</f>
+        <v/>
+      </c>
+      <c r="G19" s="20">
+        <f>DCF!$E$27/DCF!$E$5</f>
+        <v/>
+      </c>
+      <c r="H19" s="20">
+        <f>DCF!$E$27/DCF!$E$5</f>
+        <v/>
       </c>
     </row>
     <row r="20" ht="84" customHeight="1">
@@ -2205,14 +2235,17 @@
         </is>
       </c>
       <c r="D20" s="19" t="n"/>
-      <c r="F20" s="20" t="n">
-        <v>0.05971412101669879</v>
-      </c>
-      <c r="G20" s="20" t="n">
-        <v>0.05971412101669879</v>
-      </c>
-      <c r="H20" s="20" t="n">
-        <v>0.05971412101669879</v>
+      <c r="F20" s="20">
+        <f>DCF!$E$29/DCF!$E$5</f>
+        <v/>
+      </c>
+      <c r="G20" s="20">
+        <f>DCF!$E$29/DCF!$E$5</f>
+        <v/>
+      </c>
+      <c r="H20" s="20">
+        <f>DCF!$E$29/DCF!$E$5</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -2222,10 +2255,10 @@
         </is>
       </c>
       <c r="F21" s="37" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="G21" s="37" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="H21" s="37" t="n">
         <v>0</v>
@@ -7869,8 +7902,9 @@
         </is>
       </c>
       <c r="D7" s="19" t="n"/>
-      <c r="E7" s="77" t="n">
-        <v>0.566005440167168</v>
+      <c r="E7" s="77">
+        <f>(E5-E8)/E5</f>
+        <v/>
       </c>
       <c r="F7" s="20">
         <f>Scenarios!$G$14</f>
@@ -8040,7 +8074,7 @@
         </is>
       </c>
       <c r="E12" s="77" t="n">
-        <v>0.1991078666258354</v>
+        <v>0.199</v>
       </c>
       <c r="F12" s="32">
         <f>F11/F5</f>
@@ -8272,8 +8306,9 @@
         </is>
       </c>
       <c r="D20" s="19" t="n"/>
-      <c r="E20" s="88" t="n">
-        <v>6.267883648875038</v>
+      <c r="E20" s="132">
+        <f>(E21/E5)*365</f>
+        <v/>
       </c>
       <c r="F20" s="28">
         <f>Scenarios!G65</f>
@@ -8355,8 +8390,9 @@
         </is>
       </c>
       <c r="D22" s="19" t="n"/>
-      <c r="E22" s="88" t="n">
-        <v>128.8324100108167</v>
+      <c r="E22" s="132">
+        <f>(E23/E8)*365</f>
+        <v/>
       </c>
       <c r="F22" s="28">
         <f>Scenarios!G75</f>
@@ -8437,8 +8473,9 @@
         </is>
       </c>
       <c r="D24" s="19" t="n"/>
-      <c r="E24" s="88" t="n">
-        <v>25.10521290169407</v>
+      <c r="E24" s="132">
+        <f>(E25/E8)*365</f>
+        <v/>
       </c>
       <c r="F24" s="28">
         <f>Scenarios!G85</f>
@@ -8519,8 +8556,9 @@
         </is>
       </c>
       <c r="D26" s="19" t="n"/>
-      <c r="E26" s="77" t="n">
-        <v>0.05080692810692991</v>
+      <c r="E26" s="77">
+        <f>E27/E5</f>
+        <v/>
       </c>
       <c r="F26" s="20">
         <f>Scenarios!$G$19</f>
@@ -8597,8 +8635,9 @@
         </is>
       </c>
       <c r="D28" s="19" t="n"/>
-      <c r="E28" s="77" t="n">
-        <v>0.05971412101669879</v>
+      <c r="E28" s="77">
+        <f>E29/E5</f>
+        <v/>
       </c>
       <c r="F28" s="20">
         <f>Scenarios!$G$20</f>
@@ -8931,6 +8970,7 @@
         <v/>
       </c>
     </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
@@ -9173,6 +9213,8 @@
         <v/>
       </c>
     </row>
+    <row r="60"/>
+    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -9191,14 +9233,16 @@
         </is>
       </c>
     </row>
+    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
           <t>Annual repurchase budget ($000) — base case</t>
         </is>
       </c>
-      <c r="E65" s="37" t="n">
-        <v>500000</v>
+      <c r="E65" s="37">
+        <f>Scenarios!$G$21</f>
+        <v/>
       </c>
       <c r="F65" s="37">
         <f>$E$65</f>
@@ -9251,6 +9295,7 @@
         <v/>
       </c>
     </row>
+    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -9335,6 +9380,7 @@
         <v/>
       </c>
     </row>
+    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -9455,6 +9501,7 @@
         <v/>
       </c>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -9491,8 +9538,9 @@
           <t>Accretive EPS ($/share) = Net income ÷ ending shares</t>
         </is>
       </c>
-      <c r="E78" s="101" t="n">
-        <v>14.1783354282636</v>
+      <c r="E78" s="101">
+        <f>E77/E75</f>
+        <v/>
       </c>
       <c r="F78" s="101">
         <f>F77/F75</f>
@@ -9515,6 +9563,7 @@
         <v/>
       </c>
     </row>
+    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="inlineStr">
         <is>
@@ -9598,6 +9647,7 @@
         <v/>
       </c>
     </row>
+    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -9704,6 +9754,8 @@
       </c>
       <c r="D94" s="26" t="n"/>
     </row>
+    <row r="95"/>
+    <row r="96"/>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -10175,6 +10227,7 @@
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -10496,6 +10549,7 @@
         <v>407521</v>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
@@ -10582,6 +10636,7 @@
         </is>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -10632,6 +10687,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -10721,6 +10777,7 @@
         </is>
       </c>
     </row>
+    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -10867,6 +10924,7 @@
         <v/>
       </c>
     </row>
+    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>

--- a/LULU/model18_humanized.xlsx
+++ b/LULU/model18_humanized.xlsx
@@ -8073,8 +8073,9 @@
           <t>Reported EBIT margin % (incl. FY26 refund)</t>
         </is>
       </c>
-      <c r="E12" s="77" t="n">
-        <v>0.199</v>
+      <c r="E12" s="77">
+        <f>E11/E5</f>
+        <v/>
       </c>
       <c r="F12" s="32">
         <f>F11/F5</f>

--- a/LULU/model18_humanized.xlsx
+++ b/LULU/model18_humanized.xlsx
@@ -1147,14 +1147,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="B2:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1"/>
     <row r="2" ht="26" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1162,7 +1161,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -1177,7 +1175,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
@@ -1185,7 +1182,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="B9" s="5" t="inlineStr">
         <is>
@@ -1207,7 +1203,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
@@ -1225,11 +1220,9 @@
     <row r="15">
       <c r="B15" s="5" t="n"/>
     </row>
-    <row r="16"/>
     <row r="17" ht="36" customHeight="1">
       <c r="B17" s="5" t="n"/>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="B19" s="11" t="n"/>
     </row>
@@ -1334,7 +1327,6 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -1446,7 +1438,6 @@
         <v/>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
@@ -1664,7 +1655,6 @@
         <v/>
       </c>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="14" t="inlineStr">
         <is>
@@ -1700,7 +1690,6 @@
         <v/>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -2109,15 +2098,15 @@
       </c>
       <c r="D15" s="19" t="n"/>
       <c r="F15" s="131">
-        <f>(DCF!$E$21/DCF!$E$5)*365</f>
+        <f>(DCF!$E$21/$B$198)*365</f>
         <v/>
       </c>
       <c r="G15" s="131">
-        <f>(DCF!$E$21/DCF!$E$5)*365</f>
+        <f>(DCF!$E$21/$B$198)*365</f>
         <v/>
       </c>
       <c r="H15" s="131">
-        <f>(DCF!$E$21/DCF!$E$5)*365</f>
+        <f>(DCF!$E$21/$B$198)*365</f>
         <v/>
       </c>
     </row>
@@ -2210,15 +2199,15 @@
       </c>
       <c r="D19" s="19" t="n"/>
       <c r="F19" s="20">
-        <f>DCF!$E$27/DCF!$E$5</f>
+        <f>DCF!$E$27/$B$198</f>
         <v/>
       </c>
       <c r="G19" s="20">
-        <f>DCF!$E$27/DCF!$E$5</f>
+        <f>DCF!$E$27/$B$198</f>
         <v/>
       </c>
       <c r="H19" s="20">
-        <f>DCF!$E$27/DCF!$E$5</f>
+        <f>DCF!$E$27/$B$198</f>
         <v/>
       </c>
     </row>
@@ -2236,15 +2225,15 @@
       </c>
       <c r="D20" s="19" t="n"/>
       <c r="F20" s="20">
-        <f>DCF!$E$29/DCF!$E$5</f>
+        <f>DCF!$E$29/$B$198</f>
         <v/>
       </c>
       <c r="G20" s="20">
-        <f>DCF!$E$29/DCF!$E$5</f>
+        <f>DCF!$E$29/$B$198</f>
         <v/>
       </c>
       <c r="H20" s="20">
-        <f>DCF!$E$29/DCF!$E$5</f>
+        <f>DCF!$E$29/$B$198</f>
         <v/>
       </c>
     </row>
@@ -4310,15 +4299,15 @@
         </is>
       </c>
       <c r="F132" s="46">
-        <f>(F131+1807202-1798441)/111380</f>
+        <f>(F131+DCF!$E$50+DCF!$E$51)/DCF!$E$55</f>
         <v/>
       </c>
       <c r="G132" s="47">
-        <f>(G131+1807202-1798441)/111380</f>
+        <f>(G131+DCF!$E$50+DCF!$E$51)/DCF!$E$55</f>
         <v/>
       </c>
       <c r="H132" s="46">
-        <f>(H131+1807202-1798441)/111380</f>
+        <f>(H131+DCF!$E$50+DCF!$E$51)/DCF!$E$55</f>
         <v/>
       </c>
     </row>
@@ -4824,15 +4813,15 @@
         </is>
       </c>
       <c r="F163" s="42">
-        <f>1807202+F153+F158</f>
+        <f>DCF!$E$50+F153+F158</f>
         <v/>
       </c>
       <c r="G163" s="42">
-        <f>1807202+G153+G158</f>
+        <f>DCF!$E$50+G153+G158</f>
         <v/>
       </c>
       <c r="H163" s="42">
-        <f>1807202+H153+H158</f>
+        <f>DCF!$E$50+H153+H158</f>
         <v/>
       </c>
     </row>
@@ -5452,7 +5441,7 @@
     <col width="40" customWidth="1" min="9" max="9"/>
     <col width="28" customWidth="1" min="10" max="11"/>
     <col width="13" customWidth="1" min="11" max="11"/>
-    <col collapsed="1" width="36" customWidth="1" min="12" max="12"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8971,7 +8960,6 @@
         <v/>
       </c>
     </row>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
@@ -9214,8 +9202,6 @@
         <v/>
       </c>
     </row>
-    <row r="60"/>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="93" t="inlineStr">
         <is>
@@ -9234,7 +9220,6 @@
         </is>
       </c>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
@@ -9296,7 +9281,6 @@
         <v/>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
@@ -9381,7 +9365,6 @@
         <v/>
       </c>
     </row>
-    <row r="71"/>
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
@@ -9502,7 +9485,6 @@
         <v/>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
@@ -9564,7 +9546,6 @@
         <v/>
       </c>
     </row>
-    <row r="79"/>
     <row r="80">
       <c r="A80" s="93" t="inlineStr">
         <is>
@@ -9648,7 +9629,6 @@
         <v/>
       </c>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" s="93" t="inlineStr">
         <is>
@@ -9755,8 +9735,6 @@
       </c>
       <c r="D94" s="26" t="n"/>
     </row>
-    <row r="95"/>
-    <row r="96"/>
     <row r="97">
       <c r="A97" s="93" t="inlineStr">
         <is>
@@ -10228,7 +10206,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
@@ -10550,7 +10527,6 @@
         <v>407521</v>
       </c>
     </row>
-    <row r="30"/>
     <row r="31">
       <c r="A31" s="14" t="inlineStr">
         <is>
@@ -10637,7 +10613,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="14" t="inlineStr">
         <is>
@@ -10688,7 +10663,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="14" t="inlineStr">
         <is>
@@ -10778,7 +10752,6 @@
         </is>
       </c>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="14" t="inlineStr">
         <is>
@@ -10925,7 +10898,6 @@
         <v/>
       </c>
     </row>
-    <row r="61"/>
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="124" t="inlineStr">
         <is>

--- a/LULU/model18_humanized.xlsx
+++ b/LULU/model18_humanized.xlsx
@@ -30,7 +30,7 @@
     <numFmt numFmtId="169" formatCode="0.0x"/>
     <numFmt numFmtId="170" formatCode="0.0"/>
   </numFmts>
-  <fonts count="56">
+  <fonts count="58">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -361,6 +361,14 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -420,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -782,6 +790,8 @@
     <xf numFmtId="170" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2269,7 +2279,6 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
@@ -4272,7 +4281,6 @@
         <v/>
       </c>
     </row>
-    <row r="130"/>
     <row r="131">
       <c r="A131" s="23" t="inlineStr">
         <is>
@@ -4330,7 +4338,6 @@
         <v/>
       </c>
     </row>
-    <row r="134"/>
     <row r="135">
       <c r="A135" s="26" t="inlineStr">
         <is>
@@ -4338,7 +4345,6 @@
         </is>
       </c>
     </row>
-    <row r="136"/>
     <row r="137">
       <c r="A137" s="14" t="inlineStr">
         <is>
@@ -5383,10 +5389,6 @@
         </is>
       </c>
     </row>
-    <row r="194"/>
-    <row r="195"/>
-    <row r="196"/>
-    <row r="197"/>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
@@ -5468,8 +5470,34 @@
           <t>FY2025A = Historical data ingested 10-K anchors (blue). FY26–30 = red operational assumptions. Consolidated revenue cross-checks to Scenarios base case.</t>
         </is>
       </c>
+      <c r="B2" s="133" t="inlineStr">
+        <is>
+          <t>×1,000,000 (sessions in millions → count)</t>
+        </is>
+      </c>
+      <c r="C2" s="133" t="inlineStr">
+        <is>
+          <t>÷1,000 ($ → $000 on this tab)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Unit conversions (drivers)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H3" s="134" t="inlineStr">
+        <is>
+          <t>see B2/C2</t>
+        </is>
+      </c>
       <c r="I3" s="51" t="inlineStr">
         <is>
           <t>Equation (every formula row)</t>
@@ -6213,7 +6241,6 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
     <row r="22">
       <c r="A22" s="52" t="inlineStr">
         <is>
@@ -6741,7 +6768,6 @@
       </c>
       <c r="L34" s="19" t="n"/>
     </row>
-    <row r="35"/>
     <row r="36">
       <c r="A36" s="52" t="inlineStr">
         <is>
@@ -6965,7 +6991,6 @@
         </is>
       </c>
     </row>
-    <row r="42"/>
     <row r="43">
       <c r="A43" s="52" t="inlineStr">
         <is>
@@ -7349,7 +7374,6 @@
       </c>
       <c r="L51" s="19" t="n"/>
     </row>
-    <row r="52"/>
     <row r="53">
       <c r="A53" s="52" t="inlineStr">
         <is>
